--- a/public/templates/shop_performance_template.xlsx
+++ b/public/templates/shop_performance_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniel.haag/feed-checker/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4BDE0E-071E-C549-9DAF-F3C3B36F3C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CFAD3D-80DE-C34A-9307-CD51033B486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23760" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📊 Übersicht" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="🔄 Retouren &amp; Verzüge" sheetId="4" r:id="rId4"/>
     <sheet name="🛒 Sortiment" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
   <si>
     <t>Schnittstelle</t>
   </si>
@@ -334,9 +334,6 @@
   </si>
   <si>
     <t>🏆 MAXIMAL-ZIEL</t>
-  </si>
-  <si>
-    <t>hjkllhjhjhlj</t>
   </si>
   <si>
     <t>Starkes Umsatzwachstum (&gt;20% YoY)</t>
@@ -629,9 +626,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -841,6 +835,39 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -848,44 +875,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2905,310 +2902,306 @@
     </row>
     <row r="2" spans="1:5" ht="7" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
     </row>
     <row r="13" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>2024</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>19</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>2025</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>204</v>
       </c>
-      <c r="C15" s="92">
-        <v>9675770999999990</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="86"/>
+      <c r="D15" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+    </row>
+    <row r="18" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2024</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="83" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-    </row>
-    <row r="18" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="11">
-        <v>2024</v>
-      </c>
-      <c r="C18" s="11">
-        <v>2025</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>100</v>
-      </c>
-    </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="12" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="86"/>
-      <c r="C27" s="15" t="s">
+      <c r="B27" s="80"/>
+      <c r="C27" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="87"/>
+      <c r="D27" s="81"/>
     </row>
     <row r="28" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="88"/>
-      <c r="C35" s="21" t="s">
+      <c r="B35" s="82"/>
+      <c r="C35" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3229,517 +3222,517 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="32"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="33"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="33"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="33"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="32"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="33"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="38"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="37"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="43"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="37"/>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="38"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="43"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="42"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="34"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="38"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="39"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="39"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="43"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="42"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="45">
+      <c r="B25" s="44">
         <f>SUM(B4:B24)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="45">
         <f>SUM(C4:C24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="46" t="e">
+      <c r="D25" s="45" t="e">
         <f t="shared" ref="D25" si="0">C25/B25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E25" s="47"/>
+      <c r="E25" s="46"/>
     </row>
     <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
     </row>
     <row r="29" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="47" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="49">
+      <c r="A30" s="48">
         <v>1</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="53" t="e">
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52" t="e">
         <f>D30/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="54">
+      <c r="A31" s="53">
         <v>2</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58" t="e">
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="57" t="e">
         <f>D31/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="49">
+      <c r="A32" s="48">
         <v>3</v>
       </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="53" t="e">
+      <c r="B32" s="49"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="52" t="e">
         <f>D32/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="54">
+      <c r="A33" s="53">
         <v>4</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="58" t="e">
+      <c r="B33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="57" t="e">
         <f>D33/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="49">
+      <c r="A34" s="48">
         <v>5</v>
       </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="53" t="e">
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="52" t="e">
         <f>D34/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="54">
+      <c r="A35" s="53">
         <v>6</v>
       </c>
-      <c r="B35" s="55"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="58" t="e">
+      <c r="B35" s="54"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="57" t="e">
         <f>D35/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="49">
+      <c r="A36" s="48">
         <v>7</v>
       </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="53" t="e">
+      <c r="B36" s="49"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="52" t="e">
         <f>D36/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="54">
+      <c r="A37" s="53">
         <v>8</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="58" t="e">
+      <c r="B37" s="54"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57" t="e">
         <f>D37/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="49">
+      <c r="A38" s="48">
         <v>9</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="53" t="e">
+      <c r="B38" s="49"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="52" t="e">
         <f>D38/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="54">
+      <c r="A39" s="53">
         <v>10</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="58" t="e">
+      <c r="B39" s="54"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57" t="e">
         <f>D39/C25</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="79" t="s">
+      <c r="A40" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="59">
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="58">
         <f>SUM(D30:D39)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="60" t="e">
+      <c r="E40" s="59" t="e">
         <f>SUM(E30:E39)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="78" t="s">
+      <c r="A43" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
+      <c r="B43" s="88"/>
+      <c r="C43" s="88"/>
+      <c r="D43" s="88"/>
+      <c r="E43" s="88"/>
+      <c r="F43" s="88"/>
     </row>
     <row r="44" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C44" s="48" t="s">
+      <c r="C44" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="47" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="49">
+      <c r="A45" s="48">
         <v>1</v>
       </c>
-      <c r="B45" s="50"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="53" t="e">
+      <c r="B45" s="49"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="52" t="e">
         <f>D45/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="54">
+      <c r="A46" s="53">
         <v>2</v>
       </c>
-      <c r="B46" s="55"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="58" t="e">
+      <c r="B46" s="54"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="57" t="e">
         <f>D46/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="49">
+      <c r="A47" s="48">
         <v>3</v>
       </c>
-      <c r="B47" s="50"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="53" t="e">
+      <c r="B47" s="49"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="52" t="e">
         <f>D47/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="54">
+      <c r="A48" s="53">
         <v>4</v>
       </c>
-      <c r="B48" s="55"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="58" t="e">
+      <c r="B48" s="54"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="57" t="e">
         <f>D48/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="49">
+      <c r="A49" s="48">
         <v>5</v>
       </c>
-      <c r="B49" s="50"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="53" t="e">
+      <c r="B49" s="49"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="52" t="e">
         <f>D49/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="54">
+      <c r="A50" s="53">
         <v>6</v>
       </c>
-      <c r="B50" s="55"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="58" t="e">
+      <c r="B50" s="54"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="57" t="e">
         <f>D50/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="49">
+      <c r="A51" s="48">
         <v>7</v>
       </c>
-      <c r="B51" s="50"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="53" t="e">
+      <c r="B51" s="49"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="52" t="e">
         <f>D51/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="54">
+      <c r="A52" s="53">
         <v>8</v>
       </c>
-      <c r="B52" s="55"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="58" t="e">
+      <c r="B52" s="54"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="57" t="e">
         <f>D52/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="49">
+      <c r="A53" s="48">
         <v>9</v>
       </c>
-      <c r="B53" s="50"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="53" t="e">
+      <c r="B53" s="49"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="52" t="e">
         <f>D53/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="54">
+      <c r="A54" s="53">
         <v>10</v>
       </c>
-      <c r="B54" s="55"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="57"/>
-      <c r="E54" s="58" t="e">
+      <c r="B54" s="54"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="57" t="e">
         <f>D54/SUM(D45:D54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="79" t="s">
+      <c r="A55" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="79"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="59">
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="58">
         <f>SUM(D45:D54)</f>
         <v>0</v>
       </c>
-      <c r="E55" s="60" t="e">
+      <c r="E55" s="59" t="e">
         <f>SUM(E45:E54)</f>
         <v>#DIV/0!</v>
       </c>
@@ -3772,353 +3765,353 @@
   <sheetData>
     <row r="1" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
     </row>
     <row r="3" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="16" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
     </row>
     <row r="17" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="23" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="12"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="13"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="12"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="13"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="12"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="13"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="12"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="13"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="12"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="13"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="12"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="13"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
     </row>
     <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="12"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
     </row>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="13"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
     </row>
     <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="12"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
     </row>
     <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="13"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
     </row>
     <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="12"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
     </row>
     <row r="35" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="13"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
     </row>
     <row r="36" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="12"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
     </row>
     <row r="37" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="13"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="62"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
     </row>
     <row r="38" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="12"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
     </row>
     <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="13"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="12"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
     </row>
     <row r="41" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="13"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="62"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
     </row>
     <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="12"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
     </row>
     <row r="43" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="13"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="61"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="61"/>
     </row>
     <row r="44" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="12"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
     </row>
     <row r="45" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="13"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="62"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61"/>
     </row>
     <row r="46" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="12"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
     </row>
     <row r="47" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="13"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="61"/>
+      <c r="E47" s="61"/>
+      <c r="F47" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4146,144 +4139,144 @@
   <sheetData>
     <row r="1" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
     </row>
     <row r="3" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="63"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="62"/>
     </row>
     <row r="7" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="64"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="63"/>
     </row>
     <row r="8" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="63"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="62"/>
     </row>
     <row r="9" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
     </row>
     <row r="10" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="63"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="62"/>
     </row>
     <row r="11" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="64"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="63"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="62"/>
     </row>
     <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
     </row>
     <row r="16" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
     </row>
     <row r="17" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="65"/>
+      <c r="D17" s="64"/>
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="66"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="65"/>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="67"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="66"/>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="66"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="65"/>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="67"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="66"/>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="66"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="65"/>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4309,77 +4302,77 @@
   <sheetData>
     <row r="1" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
     </row>
     <row r="3" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="63"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="62"/>
     </row>
     <row r="7" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="73"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="72"/>
     </row>
     <row r="8" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="73"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="72"/>
     </row>
     <row r="9" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="76"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="75"/>
     </row>
     <row r="10" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="76"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="75"/>
     </row>
     <row r="11" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="6"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="64"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="13" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="3">
